--- a/tests/TeamworkDB/output/utilization_failures_report_202605.xlsx
+++ b/tests/TeamworkDB/output/utilization_failures_report_202605.xlsx
@@ -598,14 +598,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
   </cols>
@@ -665,37 +665,37 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>CRCH</t>
+          <t>CRDC</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Officer</t>
+          <t>Manager</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Actual_Hours</t>
+          <t>Target_Hours</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>578.70</t>
+          <t>3,718.32</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>622.90</t>
+          <t>3,579.10</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>44.20</t>
+          <t>139.22</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>7.64%</t>
+          <t>3.74%</t>
         </is>
       </c>
     </row>
@@ -707,113 +707,113 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Officer</t>
+          <t>Manager</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Actual_Hours</t>
+          <t>Target_Hours</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>971.30</t>
+          <t>3,231.69</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>1,083.80</t>
+          <t>3,371.00</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>112.50</t>
+          <t>139.31</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>11.58%</t>
+          <t>4.31%</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>CRSV</t>
+          <t>CRDC</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Officer</t>
+          <t>Manager</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Actual_Hours</t>
+          <t>Target_Rev</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>339.20</t>
+          <t>3,651,311.81</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>367.50</t>
+          <t>3,522,487.00</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>28.30</t>
+          <t>128,824.81</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>8.34%</t>
+          <t>3.53%</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>CRCH</t>
+          <t>CRNY</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Officer</t>
+          <t>Manager</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Standard_Rev</t>
+          <t>Target_Rev</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>736,416.00</t>
+          <t>3,119,621.41</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>800,506.00</t>
+          <t>3,248,446.00</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>64,090.00</t>
+          <t>128,824.59</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>8.70%</t>
+          <t>4.13%</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>CRNY</t>
+          <t>CRCH</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
@@ -823,153 +823,219 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Standard_Rev</t>
+          <t>Actual_Hours</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>1,248,464.50</t>
+          <t>578.70</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>1,384,590.00</t>
+          <t>622.90</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>136,125.50</t>
+          <t>44.20</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>10.90%</t>
+          <t>7.64%</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
+          <t>CRDC</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Actual_Hours</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>3,801.00</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>3,662.40</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>138.60</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>3.65%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>CRNY</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Actual_Hours</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>3,279.90</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>3,418.50</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>138.60</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>4.23%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>CRNY</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Officer</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Actual_Hours</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>971.30</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>1,083.80</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>112.50</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>11.58%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
           <t>CRSV</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>Officer</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>Standard_Rev</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>431,386.00</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>471,006.00</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>39,620.00</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>9.18%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>Sheet: 2026_US (YTD)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>Office</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>Column</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>Util Report</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>DB</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>Diff</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>Diff%</t>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Actual_Hours</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>339.20</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>367.50</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>28.30</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>8.34%</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>CRSV</t>
+          <t>CRCH</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Manager</t>
+          <t>Officer</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Target_Hours</t>
+          <t>Standard_Rev</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>4,801.56</t>
+          <t>736,416.00</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>5,086.50</t>
+          <t>800,506.00</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>284.94</t>
+          <t>64,090.00</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>5.93%</t>
+          <t>8.70%</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>CRSV</t>
+          <t>CRDC</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
@@ -979,101 +1045,101 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Target_Rev</t>
+          <t>Standard_Rev</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>4,629,898.40</t>
+          <t>3,707,951.00</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>4,893,431.00</t>
+          <t>3,579,746.00</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>263,532.60</t>
+          <t>128,205.00</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>5.69%</t>
+          <t>3.46%</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>CRCH</t>
+          <t>CRNY</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Officer</t>
+          <t>Manager</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Actual_Hours</t>
+          <t>Standard_Rev</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>3,335.50</t>
+          <t>3,201,489.50</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>3,644.50</t>
+          <t>3,329,695.00</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>309.00</t>
+          <t>128,205.50</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>9.26%</t>
+          <t>4.00%</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>CRSV</t>
+          <t>CRNY</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Manager</t>
+          <t>Officer</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Actual_Hours</t>
+          <t>Standard_Rev</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>5,033.90</t>
+          <t>1,248,464.50</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>5,301.90</t>
+          <t>1,384,590.00</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>268.00</t>
+          <t>136,125.50</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>5.32%</t>
+          <t>10.90%</t>
         </is>
       </c>
     </row>
@@ -1090,136 +1156,514 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
+          <t>Standard_Rev</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>431,386.00</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>471,006.00</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>39,620.00</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>9.18%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Sheet: 2026_US (YTD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Util Report</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>DB</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>Diff%</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>CRDC</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>Target_Hours</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>18,937.86</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>18,182.90</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>754.96</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>3.99%</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>CRNY</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>Target_Hours</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>16,762.83</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>17,517.80</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>754.97</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>4.50%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>CRDC</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>Target_Rev</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>18,587,971.28</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>17,889,606.00</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>698,365.28</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>3.76%</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>CRNY</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>Target_Rev</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>16,197,153.70</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>16,895,519.00</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>698,365.30</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>4.31%</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>CRCH</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>Officer</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
           <t>Actual_Hours</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>3,335.50</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>3,644.50</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>309.00</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>9.26%</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>CRDC</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>Actual_Hours</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>19,126.10</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>18,449.00</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>677.10</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>3.54%</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>CRNY</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>Actual_Hours</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>16,738.00</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>17,415.10</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>677.10</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>4.05%</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>CRSV</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>Officer</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>Actual_Hours</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
         <is>
           <t>1,385.10</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="E29" s="4" t="inlineStr">
         <is>
           <t>1,575.70</t>
         </is>
       </c>
-      <c r="F18" s="4" t="inlineStr">
+      <c r="F29" s="4" t="inlineStr">
         <is>
           <t>190.60</t>
         </is>
       </c>
-      <c r="G18" s="4" t="inlineStr">
+      <c r="G29" s="4" t="inlineStr">
         <is>
           <t>13.76%</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
         <is>
           <t>CRCH</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B30" s="4" t="inlineStr">
         <is>
           <t>Officer</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C30" s="4" t="inlineStr">
         <is>
           <t>Standard_Rev</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D30" s="4" t="inlineStr">
         <is>
           <t>4,266,630.00</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="E30" s="4" t="inlineStr">
         <is>
           <t>4,714,680.00</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="F30" s="4" t="inlineStr">
         <is>
           <t>448,050.00</t>
         </is>
       </c>
-      <c r="G19" s="4" t="inlineStr">
+      <c r="G30" s="4" t="inlineStr">
         <is>
           <t>10.50%</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>CRDC</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>Standard_Rev</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>18,677,073.00</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>18,050,756.00</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>626,317.00</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t>3.35%</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>CRNY</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>Standard_Rev</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>16,388,163.50</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>17,014,481.00</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>626,317.50</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>3.82%</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>CRSV</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>Officer</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
         <is>
           <t>Standard_Rev</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>4,844,190.00</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>5,097,277.00</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>253,087.00</t>
-        </is>
-      </c>
-      <c r="G20" s="4" t="inlineStr">
-        <is>
-          <t>5.22%</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>CRSV</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>Officer</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>Standard_Rev</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D33" s="4" t="inlineStr">
         <is>
           <t>1,775,144.00</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="E33" s="4" t="inlineStr">
         <is>
           <t>2,041,984.00</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr">
+      <c r="F33" s="4" t="inlineStr">
         <is>
           <t>266,840.00</t>
         </is>
       </c>
-      <c r="G21" s="4" t="inlineStr">
+      <c r="G33" s="4" t="inlineStr">
         <is>
           <t>15.03%</t>
         </is>
@@ -1236,15 +1680,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
+    <col width="33" customWidth="1" min="5" max="5"/>
+    <col width="33" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -1453,6 +1897,180 @@
       <c r="G10" s="4" t="inlineStr">
         <is>
           <t>953.39%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>MISSING ROWS</t>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Sheet: Month - CRDC (Monthly)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>EmpNo</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN DB</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>102231</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Conell-Price, Lynn</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>Employee_name: Conell-Price, Lynn</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>OFFC: CRNY</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>Total_Billable_Hours: 138.6000</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Sheet: DC</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>EmpNo</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN DB</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>102231</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>Conell-Price, Lynn</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>Employee_name: Conell-Price, Lynn</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>OFFC: CRNY</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>Total_Billable_Hours: 138.6000</t>
+        </is>
+      </c>
+    </row>
+    <row r="21"/>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Sheet: Month - CRNY (Monthly)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>EmpNo</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN XLS</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>102231</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: 139.27</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: 138.60000000000002</t>
         </is>
       </c>
     </row>
@@ -1467,15 +2085,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G43"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
     <col width="33" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="33" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -1490,7 +2108,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Sheet: YTD - CRDC (YTD)</t>
+          <t>Sheet: YTD - CRNY (YTD)</t>
         </is>
       </c>
     </row>
@@ -1534,765 +2152,330 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>101400</t>
+          <t>5674</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Boboshko, Nikolai</t>
+          <t>Li Bergolis, Matteo</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Target_Hours</t>
+          <t>Actual_Hours</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>743.70</t>
+          <t>582.80</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>458.80</t>
+          <t>695.30</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>284.90</t>
+          <t>112.50</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>38.31%</t>
+          <t>19.30%</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>101400</t>
+          <t>5674</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Boboshko, Nikolai</t>
+          <t>Li Bergolis, Matteo</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Target_Rev</t>
+          <t>Standard_Rev</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>687,922.50</t>
+          <t>705,188.00</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>424,390.00</t>
+          <t>841,313.00</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>263,532.50</t>
+          <t>136,125.00</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>38.31%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>101400</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>Boboshko, Nikolai</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
+          <t>19.30%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7"/>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Sheet: YTD - CRSF (YTD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>EmpNo</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Util Report</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>DB</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>Diff%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>101650</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Li, Lily</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>Actual_Hours</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>717.50</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>489.40</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>228.10</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>31.79%</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>101400</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>Boboshko, Nikolai</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>Standard_Rev</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>663,687.50</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>452,695.00</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>210,992.50</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>31.79%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Sheet: YTD - CRNY (YTD)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>165.70</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>170.70</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>3.02%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>MISSING ROWS</t>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Sheet: YTD - CRDC (YTD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>EmpNo</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>Name</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>Column</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>Util Report</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>DB</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>Diff</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>Diff%</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>101437</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>Wu, Ashley</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>Target_Hours</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>772.00</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>160.00</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>612.00</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>79.27%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>101437</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>Wu, Ashley</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>Target_Rev</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>474,780.00</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>98,400.00</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>376,380.00</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="inlineStr">
-        <is>
-          <t>79.27%</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>101437</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>Wu, Ashley</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>Actual_Hours</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>784.30</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>111.60</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>672.70</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="inlineStr">
-        <is>
-          <t>85.77%</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>5674</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>Li Bergolis, Matteo</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>Actual_Hours</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>582.80</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>695.30</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>112.50</t>
-        </is>
-      </c>
-      <c r="G15" s="4" t="inlineStr">
-        <is>
-          <t>19.30%</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>101437</t>
+          <t>MISSING IN DB</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Wu, Ashley</t>
+          <t>102231</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Standard_Rev</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>482,344.50</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>68,634.00</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>413,710.50</t>
-        </is>
-      </c>
-      <c r="G16" s="4" t="inlineStr">
-        <is>
-          <t>85.77%</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>5674</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>Li Bergolis, Matteo</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>Standard_Rev</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>705,188.00</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>841,313.00</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>136,125.00</t>
-        </is>
-      </c>
-      <c r="G17" s="4" t="inlineStr">
-        <is>
-          <t>19.30%</t>
-        </is>
-      </c>
-    </row>
-    <row r="18"/>
+          <t>Conell-Price, Lynn</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>Employee_name: Conell-Price, Lynn</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>OFFC: CRNY</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>Total_Billable_Hours: 138.6000</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Sheet: DC</t>
+        </is>
+      </c>
+    </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>Sheet: YTD - CRSF (YTD)</t>
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>EmpNo</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN DB</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>102231</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>Conell-Price, Lynn</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>Employee_name: Conell-Price, Lynn</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>OFFC: CRNY</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>Total_Billable_Hours: 138.6000</t>
+        </is>
+      </c>
+    </row>
+    <row r="21"/>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Sheet: YTD - CRNY (YTD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>EmpNo</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>Column</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>Util Report</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>DB</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t>Diff</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t>Diff%</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>101650</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>Li, Lily</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>Actual_Hours</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>165.70</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>170.70</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
-      </c>
-      <c r="G21" s="4" t="inlineStr">
-        <is>
-          <t>3.02%</t>
-        </is>
-      </c>
-    </row>
-    <row r="22"/>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>MISSING ROWS</t>
-        </is>
-      </c>
-    </row>
-    <row r="24"/>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>Sheet: YTD - CRCH (YTD)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>EmpNo</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>MISSING IN XLS</t>
         </is>
       </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>101437</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>102231</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>Target_Hrs: 160.0</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>Actual_Hrs: 111.60000000000002</t>
-        </is>
-      </c>
-    </row>
-    <row r="28"/>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>Sheet: Chicago</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>EmpNo</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN XLS</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>101437</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="inlineStr">
-        <is>
-          <t>Target_Hrs: 160.0</t>
-        </is>
-      </c>
-      <c r="E31" s="5" t="inlineStr">
-        <is>
-          <t>Actual_Hrs: 111.60000000000002</t>
-        </is>
-      </c>
-    </row>
-    <row r="32"/>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>Sheet: YTD - CRDC (YTD)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>EmpNo</t>
-        </is>
-      </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN XLS</t>
-        </is>
-      </c>
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>6038</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="D35" s="5" t="inlineStr">
-        <is>
-          <t>Target_Hrs: 84.0</t>
-        </is>
-      </c>
-      <c r="E35" s="5" t="inlineStr">
-        <is>
-          <t>Actual_Hrs: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="36"/>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>Sheet: YTD - CRSV (YTD)</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="B38" s="3" t="inlineStr">
-        <is>
-          <t>EmpNo</t>
-        </is>
-      </c>
-      <c r="C38" s="3" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN XLS</t>
-        </is>
-      </c>
-      <c r="B39" s="4" t="inlineStr">
-        <is>
-          <t>101400</t>
-        </is>
-      </c>
-      <c r="C39" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="D39" s="5" t="inlineStr">
-        <is>
-          <t>Target_Hrs: 133.20000000000005</t>
-        </is>
-      </c>
-      <c r="E39" s="5" t="inlineStr">
-        <is>
-          <t>Actual_Hrs: 106.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="40"/>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>Sheet: SV</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="3" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="B42" s="3" t="inlineStr">
-        <is>
-          <t>EmpNo</t>
-        </is>
-      </c>
-      <c r="C42" s="3" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN XLS</t>
-        </is>
-      </c>
-      <c r="B43" s="4" t="inlineStr">
-        <is>
-          <t>101400</t>
-        </is>
-      </c>
-      <c r="C43" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="D43" s="5" t="inlineStr">
-        <is>
-          <t>Target_Hrs: 133.20000000000005</t>
-        </is>
-      </c>
-      <c r="E43" s="5" t="inlineStr">
-        <is>
-          <t>Actual_Hrs: 106.0</t>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: 139.27</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: 138.60000000000002</t>
         </is>
       </c>
     </row>

--- a/tests/TeamworkDB/output/utilization_failures_report_202605.xlsx
+++ b/tests/TeamworkDB/output/utilization_failures_report_202605.xlsx
@@ -598,7 +598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>CRNY</t>
+          <t>CRSV</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
@@ -939,29 +939,29 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>971.30</t>
+          <t>339.20</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>1,083.80</t>
+          <t>367.50</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>112.50</t>
+          <t>28.30</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>11.58%</t>
+          <t>8.34%</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>CRSV</t>
+          <t>CRCH</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
@@ -971,39 +971,39 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Actual_Hours</t>
+          <t>Standard_Rev</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>339.20</t>
+          <t>736,416.00</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>367.50</t>
+          <t>800,506.00</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>28.30</t>
+          <t>64,090.00</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>8.34%</t>
+          <t>8.70%</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>CRCH</t>
+          <t>CRDC</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Officer</t>
+          <t>Manager</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -1013,29 +1013,29 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>736,416.00</t>
+          <t>3,707,951.00</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>800,506.00</t>
+          <t>3,579,746.00</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>64,090.00</t>
+          <t>128,205.00</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>8.70%</t>
+          <t>3.46%</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>CRDC</t>
+          <t>CRNY</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
@@ -1050,178 +1050,178 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>3,707,951.00</t>
+          <t>3,201,489.50</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>3,579,746.00</t>
+          <t>3,329,695.00</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>128,205.00</t>
+          <t>128,205.50</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>3.46%</t>
+          <t>4.00%</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
+          <t>CRSV</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Officer</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Standard_Rev</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>431,386.00</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>471,006.00</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>39,620.00</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>9.18%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Sheet: 2026_US (YTD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Util Report</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>DB</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>Diff%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>CRDC</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>Target_Hours</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>18,937.86</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>18,182.90</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>754.96</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>3.99%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
           <t>CRNY</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>Standard_Rev</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>3,201,489.50</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>3,329,695.00</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>128,205.50</t>
-        </is>
-      </c>
-      <c r="G16" s="4" t="inlineStr">
-        <is>
-          <t>4.00%</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>CRNY</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>Officer</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>Standard_Rev</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>1,248,464.50</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>1,384,590.00</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>136,125.50</t>
-        </is>
-      </c>
-      <c r="G17" s="4" t="inlineStr">
-        <is>
-          <t>10.90%</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>CRSV</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>Officer</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>Standard_Rev</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>431,386.00</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>471,006.00</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>39,620.00</t>
-        </is>
-      </c>
-      <c r="G18" s="4" t="inlineStr">
-        <is>
-          <t>9.18%</t>
-        </is>
-      </c>
-    </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>Sheet: 2026_US (YTD)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>Office</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>Column</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>Util Report</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>DB</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>Diff</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>Diff%</t>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>Target_Hours</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>16,762.83</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>17,517.80</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>754.97</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>4.50%</t>
         </is>
       </c>
     </row>
@@ -1238,27 +1238,27 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Target_Hours</t>
+          <t>Target_Rev</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>18,937.86</t>
+          <t>18,587,971.28</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>18,182.90</t>
+          <t>17,889,606.00</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>754.96</t>
+          <t>698,365.28</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>3.99%</t>
+          <t>3.76%</t>
         </is>
       </c>
     </row>
@@ -1275,71 +1275,71 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Target_Hours</t>
+          <t>Target_Rev</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>16,762.83</t>
+          <t>16,197,153.70</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>17,517.80</t>
+          <t>16,895,519.00</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>754.97</t>
+          <t>698,365.30</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>4.50%</t>
+          <t>4.31%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>CRDC</t>
+          <t>CRCH</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Manager</t>
+          <t>Officer</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Target_Rev</t>
+          <t>Actual_Hours</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>18,587,971.28</t>
+          <t>3,335.50</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>17,889,606.00</t>
+          <t>3,644.50</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>698,365.28</t>
+          <t>309.00</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>3.76%</t>
+          <t>9.26%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>CRNY</t>
+          <t>CRDC</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
@@ -1349,39 +1349,39 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Target_Rev</t>
+          <t>Actual_Hours</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>16,197,153.70</t>
+          <t>19,126.10</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>16,895,519.00</t>
+          <t>18,449.00</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>698,365.30</t>
+          <t>677.10</t>
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>4.31%</t>
+          <t>3.54%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>CRCH</t>
+          <t>CRNY</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Officer</t>
+          <t>Manager</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -1391,34 +1391,34 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>3,335.50</t>
+          <t>16,738.00</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>3,644.50</t>
+          <t>17,415.10</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>309.00</t>
+          <t>677.10</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>9.26%</t>
+          <t>4.05%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>CRDC</t>
+          <t>CRSV</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Manager</t>
+          <t>Officer</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -1428,108 +1428,108 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>19,126.10</t>
+          <t>1,385.10</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>18,449.00</t>
+          <t>1,575.70</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>677.10</t>
+          <t>190.60</t>
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>3.54%</t>
+          <t>13.76%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>CRNY</t>
+          <t>CRCH</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Manager</t>
+          <t>Officer</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Actual_Hours</t>
+          <t>Standard_Rev</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>16,738.00</t>
+          <t>4,266,630.00</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>17,415.10</t>
+          <t>4,714,680.00</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>677.10</t>
+          <t>448,050.00</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>4.05%</t>
+          <t>10.50%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>CRSV</t>
+          <t>CRDC</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Officer</t>
+          <t>Manager</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Actual_Hours</t>
+          <t>Standard_Rev</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>1,385.10</t>
+          <t>18,677,073.00</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>1,575.70</t>
+          <t>18,050,756.00</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>190.60</t>
+          <t>626,317.00</t>
         </is>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>13.76%</t>
+          <t>3.35%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>CRCH</t>
+          <t>CRNY</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Officer</t>
+          <t>Manager</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -1539,34 +1539,34 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>4,266,630.00</t>
+          <t>16,388,163.50</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>4,714,680.00</t>
+          <t>17,014,481.00</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>448,050.00</t>
+          <t>626,317.50</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>10.50%</t>
+          <t>3.82%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>CRDC</t>
+          <t>CRSV</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Manager</t>
+          <t>Officer</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -1576,94 +1576,20 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>18,677,073.00</t>
+          <t>1,775,144.00</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>18,050,756.00</t>
+          <t>2,041,984.00</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>626,317.00</t>
+          <t>266,840.00</t>
         </is>
       </c>
       <c r="G31" s="4" t="inlineStr">
-        <is>
-          <t>3.35%</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>CRNY</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>Standard_Rev</t>
-        </is>
-      </c>
-      <c r="D32" s="4" t="inlineStr">
-        <is>
-          <t>16,388,163.50</t>
-        </is>
-      </c>
-      <c r="E32" s="4" t="inlineStr">
-        <is>
-          <t>17,014,481.00</t>
-        </is>
-      </c>
-      <c r="F32" s="4" t="inlineStr">
-        <is>
-          <t>626,317.50</t>
-        </is>
-      </c>
-      <c r="G32" s="4" t="inlineStr">
-        <is>
-          <t>3.82%</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>CRSV</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>Officer</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>Standard_Rev</t>
-        </is>
-      </c>
-      <c r="D33" s="4" t="inlineStr">
-        <is>
-          <t>1,775,144.00</t>
-        </is>
-      </c>
-      <c r="E33" s="4" t="inlineStr">
-        <is>
-          <t>2,041,984.00</t>
-        </is>
-      </c>
-      <c r="F33" s="4" t="inlineStr">
-        <is>
-          <t>266,840.00</t>
-        </is>
-      </c>
-      <c r="G33" s="4" t="inlineStr">
         <is>
           <t>15.03%</t>
         </is>
@@ -1684,12 +1610,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="36" customWidth="1" min="4" max="4"/>
     <col width="33" customWidth="1" min="5" max="5"/>
     <col width="33" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1829,12 +1755,12 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>5674</t>
+          <t>1379</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Li Bergolis, Matteo</t>
+          <t>Bickford, Eric</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -1844,34 +1770,34 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>11.80</t>
+          <t>28.40</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>124.30</t>
+          <t>29.60</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>112.50</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>953.39%</t>
+          <t>4.23%</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>5674</t>
+          <t>1379</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Li Bergolis, Matteo</t>
+          <t>Bickford, Eric</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -1881,22 +1807,22 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>14,278.00</t>
+          <t>35,926.00</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>150,403.00</t>
+          <t>37,444.00</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>136,125.00</t>
+          <t>1,518.00</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>953.39%</t>
+          <t>4.23%</t>
         </is>
       </c>
     </row>
@@ -2085,16 +2011,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="36" customWidth="1" min="4" max="4"/>
     <col width="33" customWidth="1" min="5" max="5"/>
     <col width="33" customWidth="1" min="6" max="6"/>
-    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2108,7 +2034,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Sheet: YTD - CRNY (YTD)</t>
+          <t>Sheet: YTD - CRSF (YTD)</t>
         </is>
       </c>
     </row>
@@ -2152,12 +2078,12 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>5674</t>
+          <t>101650</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Li Bergolis, Matteo</t>
+          <t>Li, Lily</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -2167,313 +2093,246 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>582.80</t>
+          <t>165.70</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>695.30</t>
+          <t>170.70</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>112.50</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>19.30%</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>5674</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Li Bergolis, Matteo</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>Standard_Rev</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>705,188.00</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>841,313.00</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>136,125.00</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>19.30%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Sheet: YTD - CRSF (YTD)</t>
-        </is>
-      </c>
-    </row>
+          <t>3.02%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>MISSING ROWS</t>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Sheet: YTD - CRDC (YTD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>EmpNo</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>Column</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>Util Report</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>DB</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>Diff</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>Diff%</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>101650</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>Li, Lily</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>Actual_Hours</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>165.70</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>170.70</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>3.02%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>MISSING ROWS</t>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN DB</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>102231</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Conell-Price, Lynn</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>Employee_name: Conell-Price, Lynn</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>OFFC: CRNY</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>Total_Billable_Hours: 138.6000</t>
+        </is>
+      </c>
+    </row>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Sheet: DC</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>Sheet: YTD - CRDC (YTD)</t>
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>EmpNo</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN DB</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>102231</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Conell-Price, Lynn</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>Employee_name: Conell-Price, Lynn</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>OFFC: CRNY</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>Total_Billable_Hours: 138.6000</t>
+        </is>
+      </c>
+    </row>
+    <row r="16"/>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Sheet: YTD - CRNY (YTD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>EmpNo</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN DB</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN XLS</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>102231</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>Conell-Price, Lynn</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>Employee_name: Conell-Price, Lynn</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>OFFC: CRNY</t>
-        </is>
-      </c>
-      <c r="F16" s="5" t="inlineStr">
-        <is>
-          <t>Total_Billable_Hours: 138.6000</t>
-        </is>
-      </c>
-    </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>Sheet: DC</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: 139.27</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: 138.60000000000002</t>
+        </is>
+      </c>
+    </row>
+    <row r="20"/>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Sheet: NY</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>EmpNo</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN DB</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN XLS</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>102231</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>Conell-Price, Lynn</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="inlineStr">
-        <is>
-          <t>Employee_name: Conell-Price, Lynn</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t>OFFC: CRNY</t>
-        </is>
-      </c>
-      <c r="F20" s="5" t="inlineStr">
-        <is>
-          <t>Total_Billable_Hours: 138.6000</t>
-        </is>
-      </c>
-    </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>Sheet: YTD - CRNY (YTD)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>EmpNo</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN XLS</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>102231</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>Target_Hrs: 139.27</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr">
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>Actual_Hrs: 138.60000000000002</t>
         </is>
